--- a/data/trans_dic/IP13_R1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor</t>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,29</t>
+          <t>1,27; 7,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,51</t>
+          <t>0,95; 4,79</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,29</t>
+          <t>0,57; 7,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,23</t>
+          <t>0,51; 3,94</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,75</t>
+          <t>0,34; 4,01</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,47</t>
+          <t>0,32; 3,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,79</t>
+          <t>0,79; 4,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,12</t>
+          <t>0,79; 3,05</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,59</t>
+          <t>0,33; 3,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,49</t>
+          <t>0,33; 4,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,12</t>
+          <t>0,65; 3,2</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>0,93; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,59</t>
+          <t>0,95; 2,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,19</t>
+          <t>1,08; 2,23</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1323; 8022</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6129</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2283; 11530</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3809</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>548; 7031</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>968; 7498</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3970</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2931</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>389; 4643</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>702; 7525</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1716; 9366</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3439; 13305</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>388; 4265</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>530; 7066</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1827; 9037</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4640</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4454</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>6129; 17014</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7103; 19688</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>15195; 31415</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,68</t>
+          <t>1,29; 8,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,79</t>
+          <t>1,0; 4,91</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,36</t>
+          <t>0,57; 7,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,94</t>
+          <t>0,36; 4,23</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,01</t>
+          <t>0,35; 3,74</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,45</t>
+          <t>0,26; 3,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,29</t>
+          <t>0,76; 4,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,05</t>
+          <t>0,7; 2,94</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,57</t>
+          <t>0,32; 3,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,35</t>
+          <t>0,46; 4,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,2</t>
+          <t>0,65; 3,28</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,73</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,59</t>
+          <t>0,88; 2,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,63</t>
+          <t>0,92; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,23</t>
+          <t>1,13; 2,25</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1323; 8022</t>
+          <t>1349; 8748</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6129</t>
+          <t>0; 6144</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2283; 11530</t>
+          <t>2395; 11818</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3809</t>
+          <t>0; 3558</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>548; 7031</t>
+          <t>548; 6741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>968; 7498</t>
+          <t>680; 8054</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3970</t>
+          <t>0; 3766</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2931</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>389; 4643</t>
+          <t>400; 4322</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>702; 7525</t>
+          <t>568; 7157</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1716; 9366</t>
+          <t>1651; 10366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3439; 13305</t>
+          <t>3065; 12839</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>388; 4265</t>
+          <t>388; 4764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>530; 7066</t>
+          <t>753; 6591</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1827; 9037</t>
+          <t>1827; 9243</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4640</t>
+          <t>0; 4077</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4454</t>
+          <t>0; 4815</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6129; 17014</t>
+          <t>5763; 16653</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7103; 19688</t>
+          <t>6880; 19047</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15195; 31415</t>
+          <t>15864; 31699</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,37</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>1,34; 8,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,91</t>
+          <t>1,01; 4,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,51; 7,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,05</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,23</t>
+          <t>0,49; 4,21</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 6,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,74</t>
+          <t>0,3; 3,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,28</t>
+          <t>0,71; 4,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,75</t>
+          <t>0,53; 4,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,94</t>
+          <t>0,86; 3,4</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,99</t>
+          <t>0,49; 4,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,05</t>
+          <t>0,29; 3,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,28</t>
+          <t>0,64; 3,33</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,53</t>
+          <t>0,9; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,54</t>
+          <t>1,02; 2,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,25</t>
+          <t>1,14; 2,32</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5683</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1349; 8748</t>
+          <t>0; 6419</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6144</t>
+          <t>1375; 9000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2395; 11818</t>
+          <t>2271; 11223</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3065</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3558</t>
+          <t>467; 6832</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>548; 6741</t>
+          <t>0; 3340</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>680; 8054</t>
+          <t>921; 7911</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>455</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>988</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1443</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3766</t>
+          <t>0; 2432</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3215</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>400; 4322</t>
+          <t>336; 4207</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6889</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>568; 7157</t>
+          <t>1435; 9945</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1651; 10366</t>
+          <t>953; 7384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3065; 12839</t>
+          <t>3291; 12955</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4166</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>388; 4764</t>
+          <t>728; 7338</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>753; 6591</t>
+          <t>339; 4512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1827; 9243</t>
+          <t>1716; 8897</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>690</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4077</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 4240</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5763; 16653</t>
+          <t>6207; 18847</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6880; 19047</t>
+          <t>6334; 17908</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15864; 31699</t>
+          <t>14941; 30440</t>
         </is>
       </c>
     </row>
